--- a/output/pdf_financials_xlsx/TMQ.xlsx
+++ b/output/pdf_financials_xlsx/TMQ.xlsx
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-27.905</v>
@@ -1453,28 +1453,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-27.905</v>
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-27.905</v>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>199.368182</v>
+        <v>-199.368182</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>145.328358</v>
+        <v>-145.328358</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>227.451064</v>
+        <v>-227.451064</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>56.752941</v>
+        <v>-56.752941</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>79.433333</v>
+        <v>-79.433333</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>97.23999999999999</v>
+        <v>-97.23999999999999</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>105.52</v>
+        <v>-105.52</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>121.383333</v>
+        <v>-121.383333</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>-132.880952</v>
@@ -1857,28 +1857,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-27.905</v>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-27.905</v>
@@ -2099,28 +2099,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-9.648</v>
@@ -34443,16 +34443,16 @@
         </is>
       </c>
       <c r="J299" s="5" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="K299" s="5" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>21.849</v>
+        <v>-21.849</v>
       </c>
       <c r="M299" s="5" t="n">
-        <v>27.905</v>
+        <v>-27.905</v>
       </c>
       <c r="N299" t="inlineStr">
         <is>
@@ -44683,16 +44683,16 @@
         </is>
       </c>
       <c r="H415" s="5" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>9.532</v>
+        <v>-9.532</v>
       </c>
       <c r="J415" s="5" t="n">
-        <v>4.862</v>
+        <v>-4.862</v>
       </c>
       <c r="K415" s="5" t="n">
-        <v>21.104</v>
+        <v>-21.104</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -47269,13 +47269,13 @@
         </is>
       </c>
       <c r="G444" s="5" t="n">
-        <v>106.902</v>
+        <v>-106.902</v>
       </c>
       <c r="H444" s="5" t="n">
-        <v>24.394</v>
+        <v>-24.394</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>9.648</v>
+        <v>-9.648</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -48601,13 +48601,13 @@
         </is>
       </c>
       <c r="F459" s="5" t="n">
-        <v>97.37</v>
+        <v>-97.37</v>
       </c>
       <c r="G459" s="5" t="n">
-        <v>31.018</v>
+        <v>-31.018</v>
       </c>
       <c r="H459" s="5" t="n">
-        <v>24.394</v>
+        <v>-24.394</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -49763,13 +49763,13 @@
         </is>
       </c>
       <c r="E472" s="5" t="n">
-        <v>87.72199999999999</v>
+        <v>-87.72199999999999</v>
       </c>
       <c r="F472" s="5" t="n">
-        <v>11.336</v>
+        <v>-11.336</v>
       </c>
       <c r="G472" s="5" t="n">
-        <v>31.018</v>
+        <v>-31.018</v>
       </c>
       <c r="H472" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TMQ.xlsx
+++ b/output/pdf_financials_xlsx/TMQ.xlsx
@@ -869,49 +869,49 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>85.27</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.669</v>
+        <v>94.92</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.757</v>
+        <v>104.476</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.051</v>
+        <v>9.65</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.201</v>
+        <v>8.917999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.345</v>
+        <v>18.93</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.406</v>
+        <v>21.923</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.623</v>
+        <v>28.405</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.537</v>
+        <v>12.164</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.602</v>
+        <v>8.616</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.183</v>
+        <v>6.925</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.13</v>
+        <v>7.227</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>6.699</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.161</v>
+        <v>9.422000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -921,34 +921,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-85.27</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.669</v>
+        <v>-94.92</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.757</v>
+        <v>-104.476</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.051</v>
+        <v>-9.65</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-9.157999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.201</v>
+        <v>-8.917999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.345</v>
+        <v>-18.93</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.406</v>
+        <v>-21.923</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.623</v>
+        <v>-28.405</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.537</v>
+        <v>-12.164</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.183</v>
+        <v>-6.925</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.13</v>
+        <v>-7.227</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-6.699</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.161</v>
+        <v>-9.422000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>25.834</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>25.834</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.849</v>
+        <v>0.259</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.195</v>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -34092,7 +34092,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -46901,7 +46901,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -48414,7 +48414,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -49490,7 +49490,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E469" s="5" t="n">

--- a/output/pdf_financials_xlsx/TMQ.xlsx
+++ b/output/pdf_financials_xlsx/TMQ.xlsx
@@ -1464,11 +1464,15 @@
       <c r="E20" s="3" t="n">
         <v>-9.648</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-9.532</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-4.862</v>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H20" s="3" t="n">
         <v>-21.104</v>
@@ -1519,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.398</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.598</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -3993,34 +3997,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.846</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.742</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>4.249</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.657</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>2.354</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.852</v>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
@@ -4161,34 +4165,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.293</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
@@ -6573,13 +6577,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -6848,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -27720,7 +27724,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -28258,7 +28266,11 @@
           <t>Accretion -</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>2.53</v>
       </c>
@@ -43337,7 +43349,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -43359,10 +43375,10 @@
         </is>
       </c>
       <c r="I400" s="5" t="n">
-        <v>0.398</v>
+        <v>-0.398</v>
       </c>
       <c r="J400" s="5" t="n">
-        <v>0.598</v>
+        <v>-0.598</v>
       </c>
       <c r="K400" t="inlineStr">
         <is>
